--- a/314e-ig/output/StructureDefinition-coverage-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-coverage-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-coverage-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-coverage-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-coverage-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-coverage-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-coverage-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-coverage-314e.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2649" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2649" uniqueCount="446">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -845,7 +845,7 @@
     <t>Coverage.policyHolder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-patient|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-organization|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-relatedperson) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e|http://314e.com/fhir/StructureDefinition/organization-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -876,7 +876,7 @@
     <t>Coverage.subscriber</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -910,7 +910,7 @@
     <t>Coverage.beneficiary</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-patient) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1003,6 +1003,10 @@
   </si>
   <si>
     <t>Coverage.payor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
+</t>
   </si>
   <si>
     <t>(QI) Issuer of the policy</t>
@@ -1394,7 +1398,7 @@
     <t>Coverage.contract</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Contract) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/contract-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1737,7 +1741,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="223.85546875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="202.4609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -5424,19 +5428,19 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>264</v>
+        <v>316</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5506,24 +5510,24 @@
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5546,19 +5550,19 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5598,7 +5602,7 @@
         <v>159</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>20</v>
@@ -5607,7 +5611,7 @@
         <v>137</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5642,10 +5646,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5760,10 +5764,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5880,14 +5884,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5909,10 +5913,10 @@
         <v>133</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>150</v>
@@ -5967,7 +5971,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6002,10 +6006,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6031,14 +6035,14 @@
         <v>254</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -6066,10 +6070,10 @@
         <v>202</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
@@ -6087,7 +6091,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>88</v>
@@ -6122,10 +6126,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6151,16 +6155,16 @@
         <v>172</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -6209,7 +6213,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>88</v>
@@ -6233,21 +6237,21 @@
         <v>20</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6273,14 +6277,14 @@
         <v>172</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6329,7 +6333,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6353,24 +6357,24 @@
         <v>20</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>20</v>
@@ -6392,19 +6396,19 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6453,7 +6457,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6488,10 +6492,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6606,10 +6610,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6726,14 +6730,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6755,10 +6759,10 @@
         <v>133</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>150</v>
@@ -6813,7 +6817,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6848,10 +6852,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6877,14 +6881,14 @@
         <v>254</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -6894,7 +6898,7 @@
         <v>20</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>20</v>
@@ -6912,10 +6916,10 @@
         <v>202</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>20</v>
@@ -6933,7 +6937,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>88</v>
@@ -6968,10 +6972,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6997,16 +7001,16 @@
         <v>172</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -7055,7 +7059,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>88</v>
@@ -7079,21 +7083,21 @@
         <v>20</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7119,16 +7123,16 @@
         <v>172</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -7177,7 +7181,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7201,24 +7205,24 @@
         <v>20</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>20</v>
@@ -7240,19 +7244,19 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -7301,7 +7305,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7336,10 +7340,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7454,10 +7458,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7574,14 +7578,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7603,10 +7607,10 @@
         <v>133</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>150</v>
@@ -7661,7 +7665,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7696,10 +7700,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7725,14 +7729,14 @@
         <v>254</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -7742,7 +7746,7 @@
         <v>20</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>20</v>
@@ -7760,10 +7764,10 @@
         <v>202</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>20</v>
@@ -7781,7 +7785,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>88</v>
@@ -7816,10 +7820,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7845,16 +7849,16 @@
         <v>172</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -7903,7 +7907,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>88</v>
@@ -7927,21 +7931,21 @@
         <v>20</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7967,16 +7971,16 @@
         <v>172</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -8025,7 +8029,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8049,21 +8053,21 @@
         <v>20</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8086,17 +8090,17 @@
         <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8145,7 +8149,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8180,10 +8184,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8209,14 +8213,14 @@
         <v>172</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -8265,7 +8269,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8289,7 +8293,7 @@
         <v>20</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>20</v>
@@ -8300,14 +8304,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8326,19 +8330,19 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -8387,7 +8391,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8422,10 +8426,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8540,10 +8544,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8660,14 +8664,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8689,10 +8693,10 @@
         <v>133</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>150</v>
@@ -8747,7 +8751,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8782,10 +8786,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8811,16 +8815,16 @@
         <v>254</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -8848,10 +8852,10 @@
         <v>202</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>20</v>
@@ -8869,7 +8873,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8904,10 +8908,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8930,19 +8934,19 @@
         <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -8991,7 +8995,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>88</v>
@@ -9015,21 +9019,21 @@
         <v>20</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9052,17 +9056,17 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -9111,7 +9115,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9146,10 +9150,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9264,10 +9268,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9384,14 +9388,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9413,10 +9417,10 @@
         <v>133</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>150</v>
@@ -9471,7 +9475,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9506,10 +9510,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9535,14 +9539,14 @@
         <v>254</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>20</v>
@@ -9567,13 +9571,13 @@
         <v>20</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>20</v>
@@ -9591,7 +9595,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>88</v>
@@ -9626,10 +9630,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9655,14 +9659,14 @@
         <v>306</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -9711,7 +9715,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9746,10 +9750,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9772,19 +9776,19 @@
         <v>20</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>20</v>
@@ -9833,7 +9837,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9868,10 +9872,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9894,17 +9898,17 @@
         <v>20</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
@@ -9953,7 +9957,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9980,7 +9984,7 @@
         <v>270</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>272</v>

--- a/314e-ig/output/StructureDefinition-coverage-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-coverage-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-coverage-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-coverage-314e.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$69</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2649" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2687" uniqueCount="451">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -474,6 +474,22 @@
   <si>
     <t xml:space="preserve">ele-1
 </t>
+  </si>
+  <si>
+    <t>Coverage.extension:note</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/coverage-note-314e}
+</t>
+  </si>
+  <si>
+    <t>Additional notes that apply to this resource</t>
+  </si>
+  <si>
+    <t>Additional notes that apply to this resource or element.</t>
   </si>
   <si>
     <t>Coverage.modifierExtension</t>
@@ -1728,7 +1744,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP68"/>
+  <dimension ref="A1:AP69"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="46.69140625" customWidth="true" bestFit="true"/>
@@ -2981,11 +2997,13 @@
         <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="D11" t="s" s="2">
-        <v>147</v>
+        <v>20</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2998,26 +3016,22 @@
         <v>20</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N11" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="O11" t="s" s="2">
-        <v>151</v>
-      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>20</v>
       </c>
@@ -3065,7 +3079,7 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -3074,7 +3088,7 @@
         <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>20</v>
+        <v>145</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>139</v>
@@ -3083,7 +3097,7 @@
         <v>20</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>131</v>
+        <v>20</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>20</v>
@@ -3100,14 +3114,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>20</v>
+        <v>152</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3117,28 +3131,28 @@
         <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I12" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I12" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="J12" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="O12" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>20</v>
@@ -3175,17 +3189,19 @@
         <v>20</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="AC12" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3197,37 +3213,35 @@
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>162</v>
+        <v>20</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>163</v>
+        <v>20</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>165</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>167</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
         <v>20</v>
       </c>
@@ -3236,7 +3250,7 @@
         <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>89</v>
@@ -3248,19 +3262,19 @@
         <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>20</v>
@@ -3297,19 +3311,17 @@
         <v>20</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="AC13" s="2"/>
       <c r="AD13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -3318,38 +3330,40 @@
         <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>169</v>
+        <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="AP13" t="s" s="2">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="C14" s="2"/>
+        <v>158</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="D14" t="s" s="2">
         <v>20</v>
       </c>
@@ -3361,25 +3375,29 @@
         <v>88</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>173</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="O14" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
       </c>
@@ -3427,56 +3445,56 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>20</v>
+        <v>174</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>20</v>
+        <v>165</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>20</v>
+        <v>167</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>20</v>
+        <v>168</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>20</v>
+        <v>169</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>20</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>147</v>
+        <v>20</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -3488,17 +3506,15 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>133</v>
+        <v>177</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M15" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>20</v>
@@ -3535,37 +3551,37 @@
         <v>20</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>136</v>
+        <v>20</v>
       </c>
       <c r="AC15" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK15" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL15" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AK15" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>20</v>
@@ -3582,46 +3598,44 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>20</v>
+        <v>152</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="M16" t="s" s="2">
-        <v>186</v>
-      </c>
       <c r="N16" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>20</v>
       </c>
@@ -3645,69 +3659,69 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AM16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO16" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP16" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" hidden="true">
+      <c r="A17" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="AM16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3715,34 +3729,34 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I17" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>20</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>196</v>
+        <v>108</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>20</v>
@@ -3752,7 +3766,7 @@
         <v>20</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>201</v>
+        <v>20</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>20</v>
@@ -3767,13 +3781,13 @@
         <v>20</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>20</v>
@@ -3791,7 +3805,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3809,7 +3823,7 @@
         <v>20</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>20</v>
@@ -3818,18 +3832,18 @@
         <v>20</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>206</v>
+        <v>131</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3837,13 +3851,13 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>20</v>
@@ -3852,19 +3866,19 @@
         <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>102</v>
+        <v>201</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -3874,10 +3888,10 @@
         <v>20</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>20</v>
+        <v>206</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>213</v>
+        <v>20</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>20</v>
@@ -3889,13 +3903,13 @@
         <v>20</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>20</v>
+        <v>207</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>20</v>
+        <v>208</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>20</v>
+        <v>209</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>20</v>
@@ -3913,7 +3927,7 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3931,7 +3945,7 @@
         <v>20</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>20</v>
@@ -3940,7 +3954,7 @@
         <v>20</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>20</v>
@@ -3948,10 +3962,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3974,18 +3988,20 @@
         <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>172</v>
+        <v>102</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="O19" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
       </c>
@@ -3997,7 +4013,7 @@
         <v>20</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="U19" t="s" s="2">
         <v>20</v>
@@ -4033,7 +4049,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4051,7 +4067,7 @@
         <v>20</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>20</v>
@@ -4060,7 +4076,7 @@
         <v>20</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>20</v>
@@ -4068,10 +4084,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4094,15 +4110,17 @@
         <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>228</v>
+        <v>177</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -4115,7 +4133,7 @@
         <v>20</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>20</v>
+        <v>227</v>
       </c>
       <c r="U20" t="s" s="2">
         <v>20</v>
@@ -4151,7 +4169,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -4169,7 +4187,7 @@
         <v>20</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>20</v>
@@ -4178,7 +4196,7 @@
         <v>20</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>20</v>
@@ -4186,10 +4204,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4212,17 +4230,15 @@
         <v>89</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>239</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -4271,7 +4287,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4289,7 +4305,7 @@
         <v>20</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>20</v>
@@ -4298,18 +4314,18 @@
         <v>20</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4317,35 +4333,33 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>108</v>
+        <v>241</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="N22" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="M22" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>247</v>
-      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>20</v>
       </c>
@@ -4369,13 +4383,13 @@
         <v>20</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>189</v>
+        <v>20</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>248</v>
+        <v>20</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>249</v>
+        <v>20</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>20</v>
@@ -4393,10 +4407,10 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>88</v>
@@ -4408,19 +4422,19 @@
         <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>252</v>
+        <v>20</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>20</v>
+        <v>247</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>20</v>
@@ -4428,10 +4442,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4439,7 +4453,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>88</v>
@@ -4448,25 +4462,25 @@
         <v>89</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>254</v>
+        <v>108</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -4491,13 +4505,13 @@
         <v>20</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>20</v>
@@ -4515,10 +4529,10 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>88</v>
@@ -4530,30 +4544,30 @@
         <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>20</v>
+        <v>255</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>20</v>
+        <v>256</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>262</v>
+        <v>20</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4567,7 +4581,7 @@
         <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>20</v>
@@ -4576,19 +4590,19 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -4613,13 +4627,13 @@
         <v>20</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>20</v>
+        <v>207</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>20</v>
+        <v>264</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>20</v>
+        <v>265</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>20</v>
@@ -4637,7 +4651,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4658,24 +4672,24 @@
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>270</v>
+        <v>20</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>272</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4698,19 +4712,19 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4759,7 +4773,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4780,24 +4794,24 @@
         <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4811,7 +4825,7 @@
         <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>20</v>
@@ -4820,7 +4834,7 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>172</v>
+        <v>279</v>
       </c>
       <c r="L26" t="s" s="2">
         <v>280</v>
@@ -4881,7 +4895,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4890,7 +4904,7 @@
         <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>169</v>
+        <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>100</v>
@@ -4902,16 +4916,16 @@
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="27">
@@ -4927,7 +4941,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>88</v>
@@ -4942,19 +4956,19 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -5006,42 +5020,42 @@
         <v>284</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>20</v>
+        <v>174</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>290</v>
+        <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5049,13 +5063,13 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>20</v>
@@ -5064,19 +5078,19 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>172</v>
+        <v>290</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -5125,10 +5139,10 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>88</v>
@@ -5140,30 +5154,30 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>20</v>
+        <v>295</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>20</v>
+        <v>274</v>
       </c>
       <c r="AN28" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AO28" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AP28" t="s" s="2">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="29" hidden="true">
+      <c r="A29" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AO28" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="2">
-        <v>298</v>
-      </c>
       <c r="B29" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5171,34 +5185,34 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J29" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="K29" t="s" s="2">
-        <v>254</v>
+        <v>177</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5223,11 +5237,13 @@
         <v>20</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="Y29" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="Z29" t="s" s="2">
-        <v>303</v>
+        <v>20</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>20</v>
@@ -5245,7 +5261,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5269,10 +5285,10 @@
         <v>20</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>20</v>
+        <v>302</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>20</v>
@@ -5280,10 +5296,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5291,7 +5307,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>88</v>
@@ -5303,22 +5319,22 @@
         <v>20</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5343,13 +5359,11 @@
         <v>20</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>20</v>
+        <v>308</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>20</v>
@@ -5367,7 +5381,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5382,19 +5396,19 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>311</v>
+        <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>312</v>
+        <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>313</v>
+        <v>20</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>20</v>
+        <v>309</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>314</v>
+        <v>20</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>20</v>
@@ -5402,10 +5416,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5413,7 +5427,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>88</v>
@@ -5428,19 +5442,19 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5489,13 +5503,13 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
@@ -5504,30 +5518,30 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>20</v>
+        <v>316</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>20</v>
+        <v>317</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>322</v>
+        <v>20</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>324</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5535,10 +5549,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>89</v>
@@ -5547,22 +5561,22 @@
         <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5599,22 +5613,22 @@
         <v>20</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>159</v>
+        <v>20</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>331</v>
+        <v>20</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>80</v>
@@ -5632,24 +5646,24 @@
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>20</v>
+        <v>326</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>20</v>
+        <v>327</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>20</v>
+        <v>328</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>20</v>
+        <v>329</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5660,10 +5674,10 @@
         <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>20</v>
@@ -5672,16 +5686,20 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>172</v>
+        <v>331</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>173</v>
+        <v>332</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>335</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
       </c>
@@ -5717,37 +5735,37 @@
         <v>20</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>20</v>
+        <v>164</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>20</v>
+        <v>336</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>175</v>
+        <v>330</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>176</v>
+        <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>20</v>
@@ -5764,21 +5782,21 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>147</v>
+        <v>20</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -5790,17 +5808,15 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>133</v>
+        <v>177</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M34" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -5849,25 +5865,25 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>20</v>
@@ -5884,14 +5900,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>335</v>
+        <v>152</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5904,26 +5920,24 @@
         <v>20</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>336</v>
+        <v>184</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>337</v>
+        <v>185</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>20</v>
       </c>
@@ -5971,7 +5985,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>338</v>
+        <v>187</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5989,7 +6003,7 @@
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>131</v>
+        <v>181</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>20</v>
@@ -6013,36 +6027,38 @@
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>20</v>
+        <v>340</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J36" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>254</v>
+        <v>133</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="O36" t="s" s="2">
-        <v>342</v>
+        <v>156</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -6067,49 +6083,49 @@
         <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>202</v>
+        <v>20</v>
       </c>
       <c r="Y36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF36" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="Z36" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>339</v>
-      </c>
       <c r="AG36" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>20</v>
+        <v>131</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>20</v>
@@ -6126,10 +6142,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6152,19 +6168,17 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>172</v>
+        <v>259</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" s="2"/>
+      <c r="O37" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -6189,13 +6203,13 @@
         <v>20</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>20</v>
+        <v>207</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>20</v>
+        <v>348</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>20</v>
+        <v>349</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>20</v>
@@ -6213,7 +6227,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>88</v>
@@ -6237,21 +6251,21 @@
         <v>20</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>350</v>
+        <v>20</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>351</v>
+        <v>20</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>352</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6259,7 +6273,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>88</v>
@@ -6274,17 +6288,19 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="O38" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6333,10 +6349,10 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>88</v>
@@ -6357,25 +6373,23 @@
         <v>20</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="C39" t="s" s="2">
         <v>358</v>
       </c>
+      <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>20</v>
       </c>
@@ -6387,28 +6401,26 @@
         <v>88</v>
       </c>
       <c r="H39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J39" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I39" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J39" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="K39" t="s" s="2">
-        <v>326</v>
+        <v>177</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>359</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>330</v>
+        <v>361</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6457,13 +6469,13 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>325</v>
+        <v>358</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
@@ -6481,23 +6493,25 @@
         <v>20</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>20</v>
+        <v>355</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>20</v>
+        <v>356</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>20</v>
+        <v>357</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="C40" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="D40" t="s" s="2">
         <v>20</v>
       </c>
@@ -6509,7 +6523,7 @@
         <v>88</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>20</v>
@@ -6518,16 +6532,20 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>172</v>
+        <v>331</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>173</v>
+        <v>364</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>335</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
       </c>
@@ -6575,25 +6593,25 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>175</v>
+        <v>330</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>176</v>
+        <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>20</v>
@@ -6610,21 +6628,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>147</v>
+        <v>20</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6636,17 +6654,15 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>133</v>
+        <v>177</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M41" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6695,25 +6711,25 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>20</v>
@@ -6730,14 +6746,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>335</v>
+        <v>152</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6750,26 +6766,24 @@
         <v>20</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>336</v>
+        <v>184</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>337</v>
+        <v>185</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>20</v>
       </c>
@@ -6817,7 +6831,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>338</v>
+        <v>187</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6835,7 +6849,7 @@
         <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>131</v>
+        <v>181</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>20</v>
@@ -6852,43 +6866,45 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>339</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>20</v>
+        <v>340</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>254</v>
+        <v>133</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="O43" t="s" s="2">
-        <v>342</v>
+        <v>156</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -6898,7 +6914,7 @@
         <v>20</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>364</v>
+        <v>20</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>20</v>
@@ -6913,69 +6929,69 @@
         <v>20</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>202</v>
+        <v>20</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF43" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="Z43" t="s" s="2">
+      <c r="AG43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP43" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" hidden="true">
+      <c r="A44" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B44" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6989,7 +7005,7 @@
         <v>88</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>20</v>
@@ -6998,19 +7014,17 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>172</v>
+        <v>259</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>366</v>
+        <v>345</v>
       </c>
       <c r="M44" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -7020,7 +7034,7 @@
         <v>20</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>20</v>
+        <v>369</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>20</v>
@@ -7035,13 +7049,13 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>20</v>
+        <v>207</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>20</v>
+        <v>348</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>20</v>
+        <v>349</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -7059,7 +7073,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>88</v>
@@ -7083,21 +7097,21 @@
         <v>20</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>350</v>
+        <v>20</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>351</v>
+        <v>20</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>352</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7105,7 +7119,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>88</v>
@@ -7120,19 +7134,19 @@
         <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -7181,10 +7195,10 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>88</v>
@@ -7205,25 +7219,23 @@
         <v>20</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>372</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>20</v>
       </c>
@@ -7241,22 +7253,22 @@
         <v>20</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>326</v>
+        <v>177</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>328</v>
+        <v>360</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>329</v>
+        <v>375</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>330</v>
+        <v>361</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -7305,13 +7317,13 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>325</v>
+        <v>358</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>20</v>
@@ -7329,23 +7341,25 @@
         <v>20</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>20</v>
+        <v>355</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>20</v>
+        <v>356</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>20</v>
+        <v>357</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="C47" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="D47" t="s" s="2">
         <v>20</v>
       </c>
@@ -7357,7 +7371,7 @@
         <v>88</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>20</v>
@@ -7366,16 +7380,20 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>172</v>
+        <v>331</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>173</v>
+        <v>378</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>335</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
       </c>
@@ -7423,25 +7441,25 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>175</v>
+        <v>330</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>176</v>
+        <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>20</v>
@@ -7458,21 +7476,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>147</v>
+        <v>20</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>20</v>
@@ -7484,17 +7502,15 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>133</v>
+        <v>177</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M48" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -7543,25 +7559,25 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>20</v>
@@ -7578,14 +7594,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>335</v>
+        <v>152</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7598,26 +7614,24 @@
         <v>20</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>336</v>
+        <v>184</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>337</v>
+        <v>185</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>20</v>
       </c>
@@ -7665,7 +7679,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>338</v>
+        <v>187</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7683,7 +7697,7 @@
         <v>20</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>131</v>
+        <v>181</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>20</v>
@@ -7700,43 +7714,45 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>339</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>20</v>
+        <v>340</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J50" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>254</v>
+        <v>133</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="O50" t="s" s="2">
-        <v>342</v>
+        <v>156</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -7746,7 +7762,7 @@
         <v>20</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>378</v>
+        <v>20</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>20</v>
@@ -7761,69 +7777,69 @@
         <v>20</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>202</v>
+        <v>20</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="Z50" t="s" s="2">
+      <c r="AG50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP50" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" hidden="true">
+      <c r="A51" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="B51" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7837,7 +7853,7 @@
         <v>88</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>20</v>
@@ -7846,19 +7862,17 @@
         <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>172</v>
+        <v>259</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>380</v>
+        <v>345</v>
       </c>
       <c r="M51" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -7868,7 +7882,7 @@
         <v>20</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>20</v>
+        <v>383</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>20</v>
@@ -7883,13 +7897,13 @@
         <v>20</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>20</v>
+        <v>207</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>20</v>
+        <v>348</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>20</v>
+        <v>349</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
@@ -7907,7 +7921,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>88</v>
@@ -7931,21 +7945,21 @@
         <v>20</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>350</v>
+        <v>20</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>351</v>
+        <v>20</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>352</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7953,7 +7967,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>88</v>
@@ -7968,19 +7982,19 @@
         <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -8029,10 +8043,10 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>88</v>
@@ -8053,21 +8067,21 @@
         <v>20</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>385</v>
+        <v>358</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8081,7 +8095,7 @@
         <v>88</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>20</v>
@@ -8090,17 +8104,19 @@
         <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>386</v>
+        <v>177</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="O53" t="s" s="2">
-        <v>389</v>
+        <v>361</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8149,7 +8165,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>385</v>
+        <v>358</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8173,13 +8189,13 @@
         <v>20</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>20</v>
+        <v>355</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>297</v>
+        <v>356</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>20</v>
+        <v>357</v>
       </c>
     </row>
     <row r="54" hidden="true">
@@ -8210,17 +8226,17 @@
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>172</v>
+        <v>391</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -8293,10 +8309,10 @@
         <v>20</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>394</v>
+        <v>20</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>20</v>
+        <v>302</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>20</v>
@@ -8311,14 +8327,14 @@
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>396</v>
+        <v>20</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>20</v>
@@ -8327,22 +8343,20 @@
         <v>20</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>326</v>
+        <v>177</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" s="2"/>
+      <c r="O55" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -8397,7 +8411,7 @@
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>20</v>
@@ -8415,7 +8429,7 @@
         <v>20</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>20</v>
+        <v>399</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>20</v>
@@ -8426,21 +8440,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>20</v>
+        <v>401</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>20</v>
@@ -8452,16 +8466,20 @@
         <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>172</v>
+        <v>331</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>173</v>
+        <v>402</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
       </c>
@@ -8509,25 +8527,25 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>175</v>
+        <v>400</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>176</v>
+        <v>20</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>20</v>
@@ -8544,21 +8562,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>147</v>
+        <v>20</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>20</v>
@@ -8570,17 +8588,15 @@
         <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>133</v>
+        <v>177</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M57" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -8629,25 +8645,25 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>20</v>
@@ -8664,14 +8680,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>335</v>
+        <v>152</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8684,26 +8700,24 @@
         <v>20</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>336</v>
+        <v>184</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>337</v>
+        <v>185</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>20</v>
       </c>
@@ -8751,7 +8765,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>338</v>
+        <v>187</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8769,7 +8783,7 @@
         <v>20</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>131</v>
+        <v>181</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>20</v>
@@ -8786,45 +8800,45 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>20</v>
+        <v>340</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>254</v>
+        <v>133</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>405</v>
+        <v>341</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>406</v>
+        <v>342</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>407</v>
+        <v>155</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>408</v>
+        <v>156</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -8849,13 +8863,13 @@
         <v>20</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>202</v>
+        <v>20</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>409</v>
+        <v>20</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>410</v>
+        <v>20</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>20</v>
@@ -8873,25 +8887,25 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>404</v>
+        <v>343</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>20</v>
+        <v>131</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>20</v>
@@ -8908,10 +8922,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8919,7 +8933,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>88</v>
@@ -8934,19 +8948,19 @@
         <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="N60" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -8971,13 +8985,13 @@
         <v>20</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>20</v>
+        <v>207</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>20</v>
+        <v>414</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>20</v>
+        <v>415</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>20</v>
@@ -8995,10 +9009,10 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>88</v>
@@ -9019,21 +9033,21 @@
         <v>20</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>350</v>
+        <v>20</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>351</v>
+        <v>20</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>352</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9041,10 +9055,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>20</v>
@@ -9053,10 +9067,10 @@
         <v>20</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>326</v>
+        <v>417</v>
       </c>
       <c r="L61" t="s" s="2">
         <v>418</v>
@@ -9064,9 +9078,11 @@
       <c r="M61" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="N61" s="2"/>
+      <c r="N61" t="s" s="2">
+        <v>420</v>
+      </c>
       <c r="O61" t="s" s="2">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -9115,13 +9131,13 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>20</v>
@@ -9139,21 +9155,21 @@
         <v>20</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>20</v>
+        <v>355</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>20</v>
+        <v>356</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>20</v>
+        <v>357</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9164,7 +9180,7 @@
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>20</v>
@@ -9176,16 +9192,18 @@
         <v>20</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>172</v>
+        <v>331</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>173</v>
+        <v>423</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>174</v>
+        <v>424</v>
       </c>
       <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+      <c r="O62" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
       </c>
@@ -9233,25 +9251,25 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>175</v>
+        <v>422</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>176</v>
+        <v>20</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>20</v>
@@ -9268,21 +9286,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>147</v>
+        <v>20</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>20</v>
@@ -9294,17 +9312,15 @@
         <v>20</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>133</v>
+        <v>177</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M63" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>20</v>
@@ -9353,25 +9369,25 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>20</v>
@@ -9388,14 +9404,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>335</v>
+        <v>152</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9408,26 +9424,24 @@
         <v>20</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K64" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>336</v>
+        <v>184</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>337</v>
+        <v>185</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>20</v>
       </c>
@@ -9475,7 +9489,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>338</v>
+        <v>187</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9493,7 +9507,7 @@
         <v>20</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>131</v>
+        <v>181</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>20</v>
@@ -9510,43 +9524,45 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>20</v>
+        <v>340</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J65" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>254</v>
+        <v>133</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>424</v>
+        <v>341</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="O65" t="s" s="2">
-        <v>426</v>
+        <v>156</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>20</v>
@@ -9571,13 +9587,13 @@
         <v>20</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>427</v>
+        <v>20</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>428</v>
+        <v>20</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>429</v>
+        <v>20</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>20</v>
@@ -9595,25 +9611,25 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>423</v>
+        <v>343</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>20</v>
+        <v>131</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>20</v>
@@ -9630,10 +9646,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9641,7 +9657,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>88</v>
@@ -9656,17 +9672,17 @@
         <v>89</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>306</v>
+        <v>259</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -9691,13 +9707,13 @@
         <v>20</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>20</v>
+        <v>432</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>20</v>
+        <v>433</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>20</v>
+        <v>434</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>20</v>
@@ -9715,10 +9731,10 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>88</v>
@@ -9750,10 +9766,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9773,10 +9789,10 @@
         <v>20</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>435</v>
+        <v>311</v>
       </c>
       <c r="L67" t="s" s="2">
         <v>436</v>
@@ -9784,11 +9800,9 @@
       <c r="M67" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="N67" t="s" s="2">
+      <c r="N67" s="2"/>
+      <c r="O67" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>20</v>
@@ -9837,7 +9851,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9872,10 +9886,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9886,7 +9900,7 @@
         <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>20</v>
@@ -9898,15 +9912,17 @@
         <v>20</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
         <v>444</v>
       </c>
@@ -9957,13 +9973,13 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>20</v>
@@ -9975,23 +9991,143 @@
         <v>20</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>176</v>
+        <v>20</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>270</v>
+        <v>20</v>
       </c>
       <c r="AO68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="AP68" t="s" s="2">
-        <v>272</v>
+      <c r="B69" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>277</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP68">
+  <autoFilter ref="A1:AP69">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10001,7 +10137,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI67">
+  <conditionalFormatting sqref="A2:AI68">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
